--- a/Rubics Cube.xlsx
+++ b/Rubics Cube.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Daniel\Rubics Cube\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Daniel\Dev sync\Python\RubicsCube\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50D76F6-28A3-4014-8F73-8AC6F5432798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C671DF-5C07-4913-BF3C-6840BE7F41AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E2D7D174-5815-4FAD-8B7F-0C19C55A116F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E2D7D174-5815-4FAD-8B7F-0C19C55A116F}"/>
   </bookViews>
   <sheets>
     <sheet name="CFOP (Fridrich)" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="230">
   <si>
     <t>C-F-O-P</t>
   </si>
@@ -897,12 +897,36 @@
   <si>
     <t>K0: (0, 1, 1), K1: (-1, 1, 0), K2: (0, 1, -1), K3: (1, 1, 0), K4: (1, 0, -1), K5: (-1, 0, -1), K6: (-1, 0, 1), K7: (1, 0, 1), K8: (0, -1, 1), K9: (-1, -1, 0), K10: (0, -1, -1), K11: (1, -1, 0), E0: (1, 1, 1), E1: (-1, 1, 1), E2: (-1, 1, -1), E3: (1, 1, -1), E4: (1, -1, 1), E5: (-1, -1, 1), E6: (-1, -1, -1), E7: (1, -1, -1),</t>
   </si>
+  <si>
+    <t>OV</t>
+  </si>
+  <si>
+    <t>OHR</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>OHL</t>
+  </si>
+  <si>
+    <t>OVR</t>
+  </si>
+  <si>
+    <t>OVL</t>
+  </si>
+  <si>
+    <t>OL</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,6 +992,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1412,7 +1450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1536,37 +1574,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1587,6 +1595,45 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1825,6 +1872,119 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>671080</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>15043</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>99579</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>49680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{080FC6B6-DEDA-468A-9499-B71B55AA4567}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="404040"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="404040">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+        </a:blip>
+        <a:srcRect l="19847" t="14257" r="22335" b="17980"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3719080" y="1729543"/>
+          <a:ext cx="1453815" cy="1749137"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>666749</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>15039</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>124100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>75197</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Grafik 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E13000C4-34EC-4BFC-9BDE-BD2DE21E57EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="404040"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="404040">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+        </a:blip>
+        <a:srcRect t="4762" b="6517"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5740065" y="1729539"/>
+          <a:ext cx="1482667" cy="1774658"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2654,27 +2814,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="43" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="43" t="s">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="45"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="54"/>
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="51" t="s">
         <v>74</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -2715,7 +2875,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
+      <c r="A3" s="51"/>
       <c r="B3" s="10" t="s">
         <v>62</v>
       </c>
@@ -2754,7 +2914,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="51" t="s">
         <v>75</v>
       </c>
       <c r="B4" s="13" t="s">
@@ -2795,7 +2955,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="10" t="s">
         <v>62</v>
       </c>
@@ -3001,25 +3161,25 @@
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="43" t="s">
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="45"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="54"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="51" t="s">
         <v>74</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -3052,7 +3212,7 @@
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="10" t="s">
         <v>68</v>
       </c>
@@ -3083,7 +3243,7 @@
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="51" t="s">
         <v>75</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -3116,7 +3276,7 @@
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="10" t="s">
         <v>68</v>
       </c>
@@ -3261,10 +3421,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B62B715-CE6D-44A7-9969-C0ADACE536A6}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="8" width="6.28515625" customWidth="1"/>
+    <col min="10" max="12" width="6.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -3277,8 +3441,26 @@
       <c r="D1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K1" t="s">
+        <v>224</v>
+      </c>
+      <c r="L1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>116</v>
       </c>
@@ -3291,8 +3473,26 @@
       <c r="D2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -3305,9 +3505,88 @@
       <c r="D3" t="s">
         <v>124</v>
       </c>
+      <c r="F3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K3" t="s">
+        <v>222</v>
+      </c>
+      <c r="L3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F4" s="63">
+        <v>1</v>
+      </c>
+      <c r="G4" s="62">
+        <v>0</v>
+      </c>
+      <c r="H4" s="63">
+        <v>0</v>
+      </c>
+      <c r="I4" s="43"/>
+      <c r="J4" s="63">
+        <v>3</v>
+      </c>
+      <c r="K4" s="62">
+        <v>2</v>
+      </c>
+      <c r="L4" s="63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F5" s="62">
+        <v>1</v>
+      </c>
+      <c r="G5" s="43"/>
+      <c r="H5" s="62">
+        <v>3</v>
+      </c>
+      <c r="I5" s="43"/>
+      <c r="J5" s="62">
+        <v>3</v>
+      </c>
+      <c r="K5" s="43"/>
+      <c r="L5" s="62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F6" s="63">
+        <v>2</v>
+      </c>
+      <c r="G6" s="62">
+        <v>2</v>
+      </c>
+      <c r="H6" s="63">
+        <v>3</v>
+      </c>
+      <c r="I6" s="43"/>
+      <c r="J6" s="63">
+        <v>0</v>
+      </c>
+      <c r="K6" s="62">
+        <v>0</v>
+      </c>
+      <c r="L6" s="63">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3335,10 +3614,10 @@
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="48"/>
+      <c r="E2" s="56"/>
       <c r="F2" s="1" t="s">
         <v>28</v>
       </c>
@@ -3848,268 +4127,268 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="57" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="50"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
     </row>
     <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="50"/>
-      <c r="B18" s="50" t="s">
+      <c r="A18" s="57"/>
+      <c r="B18" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
-      <c r="B19" s="50" t="s">
+      <c r="A19" s="57"/>
+      <c r="B19" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
-      <c r="B20" s="50" t="s">
+      <c r="A20" s="57"/>
+      <c r="B20" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="50"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
+      <c r="A25" s="57"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="50"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="50"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
+      <c r="A27" s="57"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
+      <c r="A29" s="57"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="51"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="61"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="51"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M32" s="39" t="s">
@@ -4117,7 +4396,7 @@
       </c>
     </row>
     <row r="33" spans="10:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M33" s="57" t="s">
+      <c r="M33" s="47" t="s">
         <v>188</v>
       </c>
       <c r="N33" s="40" t="s">
@@ -4131,20 +4410,20 @@
       </c>
     </row>
     <row r="34" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M34" s="58">
-        <v>0</v>
-      </c>
-      <c r="N34" s="56">
-        <v>0</v>
-      </c>
-      <c r="O34" s="54">
-        <v>1</v>
-      </c>
-      <c r="P34" s="55">
+      <c r="M34" s="48">
+        <v>0</v>
+      </c>
+      <c r="N34" s="46">
+        <v>0</v>
+      </c>
+      <c r="O34" s="44">
+        <v>1</v>
+      </c>
+      <c r="P34" s="45">
         <v>1</v>
       </c>
       <c r="S34" s="39" t="str">
-        <f t="shared" ref="S34:S49" si="0">N34&amp;", "&amp;O34&amp;", "&amp;P34</f>
+        <f t="shared" ref="S34:S45" si="0">N34&amp;", "&amp;O34&amp;", "&amp;P34</f>
         <v>0, 1, 1</v>
       </c>
       <c r="W34" s="39" t="s">
@@ -4160,7 +4439,7 @@
       </c>
     </row>
     <row r="35" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M35" s="59">
+      <c r="M35" s="49">
         <v>1</v>
       </c>
       <c r="N35" s="25">
@@ -4180,12 +4459,12 @@
         <v>197</v>
       </c>
       <c r="AC35" s="39" t="str">
-        <f t="shared" ref="AC35:AC56" si="1">M35&amp;": ("&amp;W35&amp;"),"</f>
+        <f t="shared" ref="AC35:AC45" si="1">M35&amp;": ("&amp;W35&amp;"),"</f>
         <v>1: (-1, 1, 0),</v>
       </c>
     </row>
     <row r="36" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M36" s="59">
+      <c r="M36" s="49">
         <v>2</v>
       </c>
       <c r="N36" s="25">
@@ -4213,7 +4492,7 @@
       </c>
     </row>
     <row r="37" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M37" s="59">
+      <c r="M37" s="49">
         <v>3</v>
       </c>
       <c r="N37" s="25">
@@ -4238,7 +4517,7 @@
       </c>
     </row>
     <row r="38" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M38" s="59">
+      <c r="M38" s="49">
         <v>4</v>
       </c>
       <c r="N38" s="25">
@@ -4263,7 +4542,7 @@
       </c>
     </row>
     <row r="39" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M39" s="59">
+      <c r="M39" s="49">
         <v>5</v>
       </c>
       <c r="N39" s="25">
@@ -4288,7 +4567,7 @@
       </c>
     </row>
     <row r="40" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M40" s="59">
+      <c r="M40" s="49">
         <v>6</v>
       </c>
       <c r="N40" s="25">
@@ -4313,7 +4592,7 @@
       </c>
     </row>
     <row r="41" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M41" s="59">
+      <c r="M41" s="49">
         <v>7</v>
       </c>
       <c r="N41" s="25">
@@ -4338,7 +4617,7 @@
       </c>
     </row>
     <row r="42" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M42" s="59">
+      <c r="M42" s="49">
         <v>8</v>
       </c>
       <c r="N42" s="25">
@@ -4363,7 +4642,7 @@
       </c>
     </row>
     <row r="43" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M43" s="59">
+      <c r="M43" s="49">
         <v>9</v>
       </c>
       <c r="N43" s="25">
@@ -4388,7 +4667,7 @@
       </c>
     </row>
     <row r="44" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M44" s="59">
+      <c r="M44" s="49">
         <v>10</v>
       </c>
       <c r="N44" s="25">
@@ -4413,7 +4692,7 @@
       </c>
     </row>
     <row r="45" spans="10:31" x14ac:dyDescent="0.25">
-      <c r="M45" s="59">
+      <c r="M45" s="49">
         <v>11</v>
       </c>
       <c r="N45" s="25">
@@ -4442,7 +4721,7 @@
         <f>100+M46</f>
         <v>200</v>
       </c>
-      <c r="M46" s="59">
+      <c r="M46" s="49">
         <v>100</v>
       </c>
       <c r="N46" s="25">
@@ -4462,16 +4741,16 @@
         <v>208</v>
       </c>
       <c r="AC46" s="39" t="str">
-        <f>M46&amp;": ("&amp;W46&amp;"),"</f>
+        <f t="shared" ref="AC46:AC53" si="2">M46&amp;": ("&amp;W46&amp;"),"</f>
         <v>100: (1, 1, 1),</v>
       </c>
     </row>
     <row r="47" spans="10:31" x14ac:dyDescent="0.25">
       <c r="J47" s="38">
-        <f t="shared" ref="J47:J53" si="2">100+M47</f>
+        <f t="shared" ref="J47:J53" si="3">100+M47</f>
         <v>201</v>
       </c>
-      <c r="M47" s="59">
+      <c r="M47" s="49">
         <v>101</v>
       </c>
       <c r="N47" s="25">
@@ -4491,16 +4770,16 @@
         <v>209</v>
       </c>
       <c r="AC47" s="39" t="str">
-        <f>M47&amp;": ("&amp;W47&amp;"),"</f>
+        <f t="shared" si="2"/>
         <v>101: (-1, 1, 1),</v>
       </c>
     </row>
     <row r="48" spans="10:31" x14ac:dyDescent="0.25">
       <c r="J48" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>202</v>
       </c>
-      <c r="M48" s="59">
+      <c r="M48" s="49">
         <v>102</v>
       </c>
       <c r="N48" s="25">
@@ -4513,23 +4792,23 @@
         <v>-1</v>
       </c>
       <c r="S48" s="39" t="str">
-        <f t="shared" ref="S48:S53" si="3">N48&amp;", "&amp;O48&amp;", "&amp;P48</f>
+        <f t="shared" ref="S48:S53" si="4">N48&amp;", "&amp;O48&amp;", "&amp;P48</f>
         <v>-1, 1, -1</v>
       </c>
       <c r="W48" s="39" t="s">
         <v>210</v>
       </c>
       <c r="AC48" s="39" t="str">
-        <f>M48&amp;": ("&amp;W48&amp;"),"</f>
+        <f t="shared" si="2"/>
         <v>102: (-1, 1, -1),</v>
       </c>
     </row>
     <row r="49" spans="7:30" x14ac:dyDescent="0.25">
       <c r="J49" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>203</v>
       </c>
-      <c r="M49" s="59">
+      <c r="M49" s="49">
         <v>103</v>
       </c>
       <c r="N49" s="25">
@@ -4542,14 +4821,14 @@
         <v>-1</v>
       </c>
       <c r="S49" s="39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1, 1, -1</v>
       </c>
       <c r="W49" s="39" t="s">
         <v>211</v>
       </c>
       <c r="AC49" s="39" t="str">
-        <f>M49&amp;": ("&amp;W49&amp;"),"</f>
+        <f t="shared" si="2"/>
         <v>103: (1, 1, -1),</v>
       </c>
       <c r="AD49" s="39" t="s">
@@ -4558,10 +4837,10 @@
     </row>
     <row r="50" spans="7:30" x14ac:dyDescent="0.25">
       <c r="J50" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>204</v>
       </c>
-      <c r="M50" s="59">
+      <c r="M50" s="49">
         <v>104</v>
       </c>
       <c r="N50" s="25">
@@ -4574,14 +4853,14 @@
         <v>1</v>
       </c>
       <c r="S50" s="39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1, -1, 1</v>
       </c>
       <c r="W50" s="39" t="s">
         <v>212</v>
       </c>
       <c r="AC50" s="39" t="str">
-        <f>M50&amp;": ("&amp;W50&amp;"),"</f>
+        <f t="shared" si="2"/>
         <v>104: (1, -1, 1),</v>
       </c>
       <c r="AD50" s="39" t="s">
@@ -4590,10 +4869,10 @@
     </row>
     <row r="51" spans="7:30" x14ac:dyDescent="0.25">
       <c r="J51" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>205</v>
       </c>
-      <c r="M51" s="59">
+      <c r="M51" s="49">
         <v>105</v>
       </c>
       <c r="N51" s="25">
@@ -4606,14 +4885,14 @@
         <v>1</v>
       </c>
       <c r="S51" s="39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1, -1, 1</v>
       </c>
       <c r="W51" s="39" t="s">
         <v>213</v>
       </c>
       <c r="AC51" s="39" t="str">
-        <f>M51&amp;": ("&amp;W51&amp;"),"</f>
+        <f t="shared" si="2"/>
         <v>105: (-1, -1, 1),</v>
       </c>
       <c r="AD51" s="39" t="s">
@@ -4622,10 +4901,10 @@
     </row>
     <row r="52" spans="7:30" x14ac:dyDescent="0.25">
       <c r="J52" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>206</v>
       </c>
-      <c r="M52" s="59">
+      <c r="M52" s="49">
         <v>106</v>
       </c>
       <c r="N52" s="25">
@@ -4638,14 +4917,14 @@
         <v>-1</v>
       </c>
       <c r="S52" s="39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1, -1, -1</v>
       </c>
       <c r="W52" s="39" t="s">
         <v>214</v>
       </c>
       <c r="AC52" s="39" t="str">
-        <f>M52&amp;": ("&amp;W52&amp;"),"</f>
+        <f t="shared" si="2"/>
         <v>106: (-1, -1, -1),</v>
       </c>
       <c r="AD52" s="39" t="s">
@@ -4654,10 +4933,10 @@
     </row>
     <row r="53" spans="7:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J53" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>207</v>
       </c>
-      <c r="M53" s="60">
+      <c r="M53" s="50">
         <v>107</v>
       </c>
       <c r="N53" s="26">
@@ -4670,28 +4949,28 @@
         <v>-1</v>
       </c>
       <c r="S53" s="39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1, -1, -1</v>
       </c>
       <c r="W53" s="39" t="s">
         <v>215</v>
       </c>
       <c r="AC53" s="39" t="str">
-        <f>M53&amp;": ("&amp;W53&amp;"),"</f>
+        <f t="shared" si="2"/>
         <v>107: (1, -1, -1),</v>
       </c>
     </row>
     <row r="59" spans="7:30" x14ac:dyDescent="0.25">
-      <c r="H59" s="52" t="s">
+      <c r="H59" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="I59" s="52"/>
-      <c r="J59" s="52"/>
-      <c r="N59" s="52" t="s">
+      <c r="I59" s="60"/>
+      <c r="J59" s="60"/>
+      <c r="N59" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="O59" s="52"/>
-      <c r="P59" s="52"/>
+      <c r="O59" s="60"/>
+      <c r="P59" s="60"/>
       <c r="U59" s="39" t="s">
         <v>153</v>
       </c>
@@ -4714,38 +4993,38 @@
       </c>
     </row>
     <row r="61" spans="7:30" x14ac:dyDescent="0.25">
-      <c r="H61" s="48" t="s">
+      <c r="H61" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="I61" s="48"/>
-      <c r="J61" s="48"/>
-      <c r="N61" s="48" t="s">
+      <c r="I61" s="56"/>
+      <c r="J61" s="56"/>
+      <c r="N61" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="O61" s="48"/>
-      <c r="P61" s="48"/>
-      <c r="V61" s="48" t="s">
+      <c r="O61" s="56"/>
+      <c r="P61" s="56"/>
+      <c r="V61" s="56" t="s">
         <v>147</v>
       </c>
-      <c r="W61" s="48"/>
-      <c r="X61" s="48"/>
+      <c r="W61" s="56"/>
+      <c r="X61" s="56"/>
     </row>
     <row r="62" spans="7:30" x14ac:dyDescent="0.25">
-      <c r="H62" s="53" t="s">
+      <c r="H62" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="I62" s="53"/>
-      <c r="J62" s="53"/>
-      <c r="N62" s="53" t="s">
+      <c r="I62" s="58"/>
+      <c r="J62" s="58"/>
+      <c r="N62" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="O62" s="53"/>
-      <c r="P62" s="53"/>
-      <c r="V62" s="53" t="s">
+      <c r="O62" s="58"/>
+      <c r="P62" s="58"/>
+      <c r="V62" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="W62" s="53"/>
-      <c r="X62" s="53"/>
+      <c r="W62" s="58"/>
+      <c r="X62" s="58"/>
     </row>
     <row r="63" spans="7:30" x14ac:dyDescent="0.25">
       <c r="H63" s="36">
@@ -4872,27 +5151,27 @@
       <c r="AC65" s="39">
         <v>1</v>
       </c>
-      <c r="AF65" s="49" t="s">
+      <c r="AF65" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="AG65" s="49" t="s">
+      <c r="AG65" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="AH65" s="49"/>
-      <c r="AI65" s="49" t="s">
+      <c r="AH65" s="59"/>
+      <c r="AI65" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="AJ65" s="49" t="s">
+      <c r="AJ65" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="AK65" s="49"/>
-      <c r="AL65" s="49" t="s">
+      <c r="AK65" s="59"/>
+      <c r="AL65" s="59" t="s">
         <v>219</v>
       </c>
-      <c r="AM65" s="49" t="s">
+      <c r="AM65" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="AN65" s="49"/>
+      <c r="AN65" s="59"/>
     </row>
     <row r="66" spans="7:40" x14ac:dyDescent="0.25">
       <c r="AA66" s="39" t="s">
@@ -4904,15 +5183,15 @@
       <c r="AC66" s="39">
         <v>-1</v>
       </c>
-      <c r="AF66" s="49"/>
-      <c r="AG66" s="49"/>
-      <c r="AH66" s="49"/>
-      <c r="AI66" s="49"/>
-      <c r="AJ66" s="49"/>
-      <c r="AK66" s="49"/>
-      <c r="AL66" s="49"/>
-      <c r="AM66" s="49"/>
-      <c r="AN66" s="49"/>
+      <c r="AF66" s="59"/>
+      <c r="AG66" s="59"/>
+      <c r="AH66" s="59"/>
+      <c r="AI66" s="59"/>
+      <c r="AJ66" s="59"/>
+      <c r="AK66" s="59"/>
+      <c r="AL66" s="59"/>
+      <c r="AM66" s="59"/>
+      <c r="AN66" s="59"/>
     </row>
     <row r="67" spans="7:40" x14ac:dyDescent="0.25">
       <c r="AA67" s="39" t="s">
@@ -4924,32 +5203,32 @@
       <c r="AC67" s="39">
         <v>1</v>
       </c>
-      <c r="AF67" s="49"/>
-      <c r="AG67" s="49"/>
-      <c r="AH67" s="49"/>
-      <c r="AI67" s="49"/>
-      <c r="AJ67" s="49"/>
-      <c r="AK67" s="49"/>
-      <c r="AL67" s="49"/>
-      <c r="AM67" s="49"/>
-      <c r="AN67" s="49"/>
+      <c r="AF67" s="59"/>
+      <c r="AG67" s="59"/>
+      <c r="AH67" s="59"/>
+      <c r="AI67" s="59"/>
+      <c r="AJ67" s="59"/>
+      <c r="AK67" s="59"/>
+      <c r="AL67" s="59"/>
+      <c r="AM67" s="59"/>
+      <c r="AN67" s="59"/>
     </row>
     <row r="68" spans="7:40" x14ac:dyDescent="0.25">
-      <c r="H68" s="53" t="s">
+      <c r="H68" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="I68" s="53"/>
-      <c r="J68" s="53"/>
-      <c r="N68" s="53" t="s">
+      <c r="I68" s="58"/>
+      <c r="J68" s="58"/>
+      <c r="N68" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="O68" s="53"/>
-      <c r="P68" s="53"/>
-      <c r="V68" s="53" t="s">
+      <c r="O68" s="58"/>
+      <c r="P68" s="58"/>
+      <c r="V68" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="W68" s="53"/>
-      <c r="X68" s="53"/>
+      <c r="W68" s="58"/>
+      <c r="X68" s="58"/>
       <c r="AA68" s="39" t="s">
         <v>143</v>
       </c>
@@ -5016,39 +5295,39 @@
         <v>-1</v>
       </c>
       <c r="AF69" s="39">
-        <f t="shared" ref="AF69:AF70" si="4">H69</f>
+        <f t="shared" ref="AF69:AF70" si="5">H69</f>
         <v>-1</v>
       </c>
       <c r="AG69" s="39">
-        <f t="shared" ref="AG69:AG70" si="5">N69</f>
+        <f t="shared" ref="AG69:AG70" si="6">N69</f>
         <v>1</v>
       </c>
       <c r="AH69" s="39">
-        <f t="shared" ref="AH69:AH70" si="6">V69</f>
+        <f t="shared" ref="AH69:AH70" si="7">V69</f>
         <v>-1</v>
       </c>
       <c r="AI69" s="39">
-        <f t="shared" ref="AI69:AI70" si="7">I69</f>
+        <f t="shared" ref="AI69:AI70" si="8">I69</f>
         <v>0</v>
       </c>
       <c r="AJ69" s="39">
-        <f t="shared" ref="AJ69" si="8">O69</f>
+        <f t="shared" ref="AJ69" si="9">O69</f>
         <v>1</v>
       </c>
       <c r="AK69" s="39">
-        <f t="shared" ref="AK69:AK70" si="9">W69</f>
+        <f t="shared" ref="AK69:AK70" si="10">W69</f>
         <v>-1</v>
       </c>
       <c r="AL69" s="39">
-        <f t="shared" ref="AL69:AL70" si="10">J69</f>
+        <f t="shared" ref="AL69:AL70" si="11">J69</f>
         <v>1</v>
       </c>
       <c r="AM69" s="39">
-        <f t="shared" ref="AM69:AM70" si="11">P69</f>
+        <f t="shared" ref="AM69:AM70" si="12">P69</f>
         <v>1</v>
       </c>
       <c r="AN69" s="39">
-        <f t="shared" ref="AN69:AN70" si="12">X69</f>
+        <f t="shared" ref="AN69:AN70" si="13">X69</f>
         <v>-1</v>
       </c>
     </row>
@@ -5099,19 +5378,19 @@
         <v>76</v>
       </c>
       <c r="AF70" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="AG70" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AH70" s="39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AI70" s="39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ70" s="39">
@@ -5119,19 +5398,19 @@
         <v>1</v>
       </c>
       <c r="AK70" s="39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AL70" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="AM70" s="39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AN70" s="39">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5201,21 +5480,21 @@
       </c>
     </row>
     <row r="73" spans="7:40" x14ac:dyDescent="0.25">
-      <c r="H73" s="53" t="s">
+      <c r="H73" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="I73" s="53"/>
-      <c r="J73" s="53"/>
-      <c r="N73" s="53" t="s">
+      <c r="I73" s="58"/>
+      <c r="J73" s="58"/>
+      <c r="N73" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="O73" s="53"/>
-      <c r="P73" s="53"/>
-      <c r="V73" s="53" t="s">
+      <c r="O73" s="58"/>
+      <c r="P73" s="58"/>
+      <c r="V73" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="W73" s="53"/>
-      <c r="X73" s="53"/>
+      <c r="W73" s="58"/>
+      <c r="X73" s="58"/>
     </row>
     <row r="74" spans="7:40" x14ac:dyDescent="0.25">
       <c r="H74" s="36">
@@ -5250,11 +5529,11 @@
         <v>-1, 1, -1</v>
       </c>
       <c r="AI74" s="39" t="str">
-        <f t="shared" ref="AI74" si="13">AI69&amp;", "&amp;AJ69&amp;", "&amp;AK69</f>
+        <f t="shared" ref="AI74" si="14">AI69&amp;", "&amp;AJ69&amp;", "&amp;AK69</f>
         <v>0, 1, -1</v>
       </c>
       <c r="AL74" s="39" t="str">
-        <f t="shared" ref="AL74:AL76" si="14">AL69&amp;", "&amp;AM69&amp;", "&amp;AN69</f>
+        <f t="shared" ref="AL74:AL76" si="15">AL69&amp;", "&amp;AM69&amp;", "&amp;AN69</f>
         <v>1, 1, -1</v>
       </c>
     </row>
@@ -5303,11 +5582,11 @@
         <v>-1, 1, 0</v>
       </c>
       <c r="AI75" s="39" t="str">
-        <f t="shared" ref="AI75" si="15">AI70&amp;", "&amp;AJ70&amp;", "&amp;AK70</f>
+        <f t="shared" ref="AI75" si="16">AI70&amp;", "&amp;AJ70&amp;", "&amp;AK70</f>
         <v>0, 1, 0</v>
       </c>
       <c r="AL75" s="39" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1, 1, 0</v>
       </c>
     </row>
@@ -5344,11 +5623,11 @@
         <v>-1, 1, 1</v>
       </c>
       <c r="AI76" s="39" t="str">
-        <f t="shared" ref="AI76" si="16">AI71&amp;", "&amp;AJ71&amp;", "&amp;AK71</f>
+        <f t="shared" ref="AI76" si="17">AI71&amp;", "&amp;AJ71&amp;", "&amp;AK71</f>
         <v>0, 1, 1</v>
       </c>
       <c r="AL76" s="39" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1, 1, 1</v>
       </c>
     </row>
@@ -5896,6 +6175,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="AM65:AM67"/>
+    <mergeCell ref="AN65:AN67"/>
+    <mergeCell ref="AG65:AG67"/>
+    <mergeCell ref="AH65:AH67"/>
+    <mergeCell ref="AI65:AI67"/>
+    <mergeCell ref="AJ65:AJ67"/>
+    <mergeCell ref="AK65:AK67"/>
+    <mergeCell ref="AL65:AL67"/>
+    <mergeCell ref="AF65:AF67"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="N59:P59"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="V62:X62"/>
@@ -5910,45 +6226,8 @@
     <mergeCell ref="N62:P62"/>
     <mergeCell ref="N68:P68"/>
     <mergeCell ref="N73:P73"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="AF65:AF67"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="N59:P59"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="AM65:AM67"/>
-    <mergeCell ref="AN65:AN67"/>
-    <mergeCell ref="AG65:AG67"/>
-    <mergeCell ref="AH65:AH67"/>
-    <mergeCell ref="AI65:AI67"/>
-    <mergeCell ref="AJ65:AJ67"/>
-    <mergeCell ref="AK65:AK67"/>
-    <mergeCell ref="AL65:AL67"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
